--- a/inputs/low_risk.xlsx
+++ b/inputs/low_risk.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Profesh\Forward Edge AI\Treasury AI\single-finding-fix\mdl-backend-demo\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0950E120-7597-4AA3-BAE0-7A4D17B58C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB780435-6B64-4CC9-949A-33FEB9B5807B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29250" yWindow="930" windowWidth="23175" windowHeight="14055" xr2:uid="{C0EA019A-F196-43A6-9184-C20F432BAEE8}"/>
+    <workbookView xWindow="24060" yWindow="1170" windowWidth="23175" windowHeight="14055" xr2:uid="{C0EA019A-F196-43A6-9184-C20F432BAEE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -83,9 +83,6 @@
     <t>Belmont County</t>
   </si>
   <si>
-    <t>Benton County</t>
-  </si>
-  <si>
     <t>Big Valley Rancheria Band of Pomo Indians</t>
   </si>
   <si>
@@ -131,17 +128,20 @@
     <t>CHEYENNE COUNTY, NEBRASKA</t>
   </si>
   <si>
-    <t>Chisago County</t>
-  </si>
-  <si>
     <t>City and County of Denver</t>
+  </si>
+  <si>
+    <t>City of Aberdeen</t>
+  </si>
+  <si>
+    <t>City of Alamogordo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,8 +149,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -161,6 +168,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -179,7 +192,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -535,7 +548,7 @@
       <c r="B2">
         <v>2022</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -546,7 +559,7 @@
       <c r="B3">
         <v>2024</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -557,7 +570,7 @@
       <c r="B4">
         <v>2021</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -568,7 +581,7 @@
       <c r="B5">
         <v>2023</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -579,7 +592,7 @@
       <c r="B6">
         <v>2022</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -590,7 +603,7 @@
       <c r="B7">
         <v>2024</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -601,7 +614,7 @@
       <c r="B8">
         <v>2024</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -612,7 +625,7 @@
       <c r="B9">
         <v>2023</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -623,7 +636,7 @@
       <c r="B10">
         <v>2021</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -634,7 +647,7 @@
       <c r="B11">
         <v>2023</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -645,7 +658,7 @@
       <c r="B12">
         <v>2024</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -656,19 +669,19 @@
       <c r="B13">
         <v>2023</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>416005759</v>
+      <c r="A14" s="2">
+        <v>916001226</v>
       </c>
       <c r="B14">
-        <v>2023</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>15</v>
+        <v>2021</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -678,8 +691,8 @@
       <c r="B15">
         <v>2024</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>16</v>
+      <c r="C15" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -689,8 +702,8 @@
       <c r="B16">
         <v>2023</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>17</v>
+      <c r="C16" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -700,8 +713,8 @@
       <c r="B17">
         <v>2022</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>18</v>
+      <c r="C17" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -711,8 +724,8 @@
       <c r="B18">
         <v>2024</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>19</v>
+      <c r="C18" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -722,8 +735,8 @@
       <c r="B19">
         <v>2024</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>20</v>
+      <c r="C19" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -733,8 +746,8 @@
       <c r="B20">
         <v>2023</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>21</v>
+      <c r="C20" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -744,8 +757,8 @@
       <c r="B21">
         <v>2023</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>22</v>
+      <c r="C21" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -755,8 +768,8 @@
       <c r="B22">
         <v>2023</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>23</v>
+      <c r="C22" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -766,8 +779,8 @@
       <c r="B23">
         <v>2023</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>24</v>
+      <c r="C23" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -777,8 +790,8 @@
       <c r="B24">
         <v>2024</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>25</v>
+      <c r="C24" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -788,8 +801,8 @@
       <c r="B25">
         <v>2024</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>26</v>
+      <c r="C25" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -799,8 +812,8 @@
       <c r="B26">
         <v>2025</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>27</v>
+      <c r="C26" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -810,8 +823,8 @@
       <c r="B27">
         <v>2023</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>28</v>
+      <c r="C27" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -821,8 +834,8 @@
       <c r="B28">
         <v>2022</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>29</v>
+      <c r="C28" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -832,19 +845,19 @@
       <c r="B29">
         <v>2024</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>30</v>
+      <c r="C29" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>416005772</v>
+      <c r="A30" s="2">
+        <v>856000099</v>
       </c>
       <c r="B30">
-        <v>2024</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>31</v>
+        <v>2023</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -854,8 +867,8 @@
       <c r="B31">
         <v>2024</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>32</v>
+      <c r="C31" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
